--- a/OrganizedData/Fracture_GIc_KIc_Results/Fracture_GIc_KIc_Composition_Summary.xlsx
+++ b/OrganizedData/Fracture_GIc_KIc_Results/Fracture_GIc_KIc_Composition_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="295" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="321" uniqueCount="21">
   <si>
     <t>AP_Percent</t>
   </si>
@@ -125,16 +125,16 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="true"/>
-    <col min="2" max="2" width="14.28515625" customWidth="true"/>
-    <col min="3" max="3" width="5.140625" customWidth="true"/>
-    <col min="4" max="4" width="8.5703125" customWidth="true"/>
-    <col min="5" max="5" width="18.28515625" customWidth="true"/>
-    <col min="6" max="6" width="16.140625" customWidth="true"/>
-    <col min="7" max="7" width="22.28515625" customWidth="true"/>
-    <col min="8" max="8" width="19.28515625" customWidth="true"/>
-    <col min="9" max="9" width="17.140625" customWidth="true"/>
-    <col min="10" max="10" width="23.85546875" customWidth="true"/>
+    <col min="1" max="1" width="10.36328125" customWidth="true"/>
+    <col min="2" max="2" width="13.1796875" customWidth="true"/>
+    <col min="3" max="3" width="4.90625" customWidth="true"/>
+    <col min="4" max="4" width="7.90625" customWidth="true"/>
+    <col min="5" max="5" width="17.36328125" customWidth="true"/>
+    <col min="6" max="6" width="15.1796875" customWidth="true"/>
+    <col min="7" max="7" width="20.54296875" customWidth="true"/>
+    <col min="8" max="8" width="18.36328125" customWidth="true"/>
+    <col min="9" max="9" width="16.1796875" customWidth="true"/>
+    <col min="10" max="10" width="22.1796875" customWidth="true"/>
     <col min="11" max="11" width="23.85546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -196,10 +196,10 @@
         <v>68</v>
       </c>
       <c r="H2" s="0">
-        <v>0.5558745685715607</v>
+        <v>0.55587456857156081</v>
       </c>
       <c r="I2" s="0">
-        <v>0.24877757724165872</v>
+        <v>0.24877757724165875</v>
       </c>
       <c r="J2" s="0">
         <v>68</v>
@@ -266,7 +266,7 @@
         <v>96</v>
       </c>
       <c r="H4" s="0">
-        <v>1.3275761185151738</v>
+        <v>1.3275761185151736</v>
       </c>
       <c r="I4" s="0">
         <v>0.31401244276039425</v>
@@ -374,7 +374,7 @@
         <v>0.67289734887984221</v>
       </c>
       <c r="I7" s="0">
-        <v>0.23827214134709862</v>
+        <v>0.23827214134709865</v>
       </c>
       <c r="J7" s="0">
         <v>122</v>
@@ -406,7 +406,7 @@
         <v>118</v>
       </c>
       <c r="H8" s="0">
-        <v>1.2558023508057488</v>
+        <v>1.255802350805749</v>
       </c>
       <c r="I8" s="0">
         <v>0.35681028234329498</v>
@@ -444,7 +444,7 @@
         <v>0.89020314098317222</v>
       </c>
       <c r="I9" s="0">
-        <v>0.29702976795039016</v>
+        <v>0.2970297679503901</v>
       </c>
       <c r="J9" s="0">
         <v>116</v>

--- a/OrganizedData/Fracture_GIc_KIc_Results/Fracture_GIc_KIc_Composition_Summary.xlsx
+++ b/OrganizedData/Fracture_GIc_KIc_Results/Fracture_GIc_KIc_Composition_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="321" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="373" uniqueCount="21">
   <si>
     <t>AP_Percent</t>
   </si>
@@ -125,16 +125,16 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="true"/>
-    <col min="2" max="2" width="13.1796875" customWidth="true"/>
-    <col min="3" max="3" width="4.90625" customWidth="true"/>
-    <col min="4" max="4" width="7.90625" customWidth="true"/>
-    <col min="5" max="5" width="17.36328125" customWidth="true"/>
-    <col min="6" max="6" width="15.1796875" customWidth="true"/>
-    <col min="7" max="7" width="20.54296875" customWidth="true"/>
-    <col min="8" max="8" width="18.36328125" customWidth="true"/>
-    <col min="9" max="9" width="16.1796875" customWidth="true"/>
-    <col min="10" max="10" width="22.1796875" customWidth="true"/>
+    <col min="1" max="1" width="11.42578125" customWidth="true"/>
+    <col min="2" max="2" width="14.28515625" customWidth="true"/>
+    <col min="3" max="3" width="5.140625" customWidth="true"/>
+    <col min="4" max="4" width="8.5703125" customWidth="true"/>
+    <col min="5" max="5" width="18.28515625" customWidth="true"/>
+    <col min="6" max="6" width="16.140625" customWidth="true"/>
+    <col min="7" max="7" width="22.28515625" customWidth="true"/>
+    <col min="8" max="8" width="19.28515625" customWidth="true"/>
+    <col min="9" max="9" width="17.140625" customWidth="true"/>
+    <col min="10" max="10" width="23.85546875" customWidth="true"/>
     <col min="11" max="11" width="23.85546875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -175,34 +175,34 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B2" s="0">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="0">
-        <v>2.825838625125249</v>
+        <v>3.8515419137314271</v>
       </c>
       <c r="F2" s="0">
-        <v>1.0139032983674876</v>
+        <v>0.54606686905581936</v>
       </c>
       <c r="G2" s="0">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="H2" s="0">
-        <v>0.55587456857156081</v>
+        <v>1.2558023508057488</v>
       </c>
       <c r="I2" s="0">
-        <v>0.24877757724165875</v>
+        <v>0.35681028234329498</v>
       </c>
       <c r="J2" s="0">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="K2" s="0">
         <v>68</v>
@@ -210,34 +210,34 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B3" s="0">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="0">
-        <v>2.1769813473209507</v>
+        <v>3.0426433762573924</v>
       </c>
       <c r="F3" s="0">
-        <v>0.78131438521517716</v>
+        <v>0.52510167722990497</v>
       </c>
       <c r="G3" s="0">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="H3" s="0">
-        <v>0.38404417894266479</v>
+        <v>0.89020314098317222</v>
       </c>
       <c r="I3" s="0">
-        <v>0.14698903205513456</v>
+        <v>0.29702976795039016</v>
       </c>
       <c r="J3" s="0">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="K3" s="0">
         <v>56</v>
@@ -245,34 +245,34 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B4" s="0">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="0">
-        <v>3.9141379195742054</v>
+        <v>2.825838625125249</v>
       </c>
       <c r="F4" s="0">
-        <v>0.44785783521250605</v>
+        <v>1.0139032983674876</v>
       </c>
       <c r="G4" s="0">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="H4" s="0">
-        <v>1.3275761185151736</v>
+        <v>0.5558745685715607</v>
       </c>
       <c r="I4" s="0">
-        <v>0.31401244276039425</v>
+        <v>0.24877757724165872</v>
       </c>
       <c r="J4" s="0">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="K4" s="0">
         <v>96</v>
@@ -280,34 +280,34 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B5" s="0">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="0">
-        <v>2.9826947551735832</v>
+        <v>2.1769813473209507</v>
       </c>
       <c r="F5" s="0">
-        <v>0.3408923346748915</v>
+        <v>0.78131438521517716</v>
       </c>
       <c r="G5" s="0">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="H5" s="0">
-        <v>0.67631616779126025</v>
+        <v>0.38404417894266479</v>
       </c>
       <c r="I5" s="0">
-        <v>0.15650102203479918</v>
+        <v>0.14698903205513456</v>
       </c>
       <c r="J5" s="0">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="K5" s="0">
         <v>92</v>
@@ -315,34 +315,34 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B6" s="0">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="0">
-        <v>3.3139953574222285</v>
+        <v>3.9141379195742054</v>
       </c>
       <c r="F6" s="0">
-        <v>0.37934784569341484</v>
+        <v>0.44785783521250605</v>
       </c>
       <c r="G6" s="0">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="H6" s="0">
-        <v>0.89591236360382665</v>
+        <v>1.3275761185151738</v>
       </c>
       <c r="I6" s="0">
-        <v>0.27345018123554299</v>
+        <v>0.31401244276039425</v>
       </c>
       <c r="J6" s="0">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="K6" s="0">
         <v>128</v>
@@ -350,34 +350,34 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B7" s="0">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="0">
-        <v>2.3122089134177268</v>
+        <v>2.9826947551735832</v>
       </c>
       <c r="F7" s="0">
-        <v>0.53651238128877243</v>
+        <v>0.3408923346748915</v>
       </c>
       <c r="G7" s="0">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="H7" s="0">
-        <v>0.67289734887984221</v>
+        <v>0.67631616779126025</v>
       </c>
       <c r="I7" s="0">
-        <v>0.23827214134709865</v>
+        <v>0.15650102203479918</v>
       </c>
       <c r="J7" s="0">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="K7" s="0">
         <v>122</v>
@@ -385,34 +385,34 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B8" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="0">
-        <v>3.8515419137314271</v>
+        <v>3.3139953574222285</v>
       </c>
       <c r="F8" s="0">
-        <v>0.54606686905581936</v>
+        <v>0.37934784569341484</v>
       </c>
       <c r="G8" s="0">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="H8" s="0">
-        <v>1.255802350805749</v>
+        <v>0.89591236360382665</v>
       </c>
       <c r="I8" s="0">
-        <v>0.35681028234329498</v>
+        <v>0.27345018123554299</v>
       </c>
       <c r="J8" s="0">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="K8" s="0">
         <v>118</v>
@@ -420,34 +420,34 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B9" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="0">
-        <v>3.0426433762573924</v>
+        <v>2.3122089134177268</v>
       </c>
       <c r="F9" s="0">
-        <v>0.52510167722990497</v>
+        <v>0.53651238128877243</v>
       </c>
       <c r="G9" s="0">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H9" s="0">
-        <v>0.89020314098317222</v>
+        <v>0.67289734887984221</v>
       </c>
       <c r="I9" s="0">
-        <v>0.2970297679503901</v>
+        <v>0.23827214134709862</v>
       </c>
       <c r="J9" s="0">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K9" s="0">
         <v>116</v>
